--- a/Practica3 2024.eng/times.xlsx
+++ b/Practica3 2024.eng/times.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="14">
   <si>
     <t>n</t>
   </si>
@@ -33,6 +33,39 @@
   </si>
   <si>
     <t>OoT</t>
+  </si>
+  <si>
+    <t>Substraction 4</t>
+  </si>
+  <si>
+    <t>Substraction 5</t>
+  </si>
+  <si>
+    <t>division4</t>
+  </si>
+  <si>
+    <t>division5</t>
+  </si>
+  <si>
+    <t>VectorSum</t>
+  </si>
+  <si>
+    <t>Sum1</t>
+  </si>
+  <si>
+    <t>Sum2</t>
+  </si>
+  <si>
+    <t>Sum3</t>
+  </si>
+  <si>
+    <t>Fibonacci</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>Time</t>
   </si>
 </sst>
 </file>
@@ -68,8 +101,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -350,10 +386,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:B8"/>
+  <dimension ref="A2:M63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -361,7 +401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>100</v>
       </c>
@@ -369,7 +409,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>200</v>
       </c>
@@ -377,7 +417,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>400</v>
       </c>
@@ -385,7 +425,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>800</v>
       </c>
@@ -393,7 +433,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1600</v>
       </c>
@@ -401,11 +441,888 @@
         <v>18726</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>3200</v>
       </c>
       <c r="B8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>100</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="F12">
+        <v>30</v>
+      </c>
+      <c r="G12" s="1">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <f>B12*2</f>
+        <v>200</v>
+      </c>
+      <c r="C13">
+        <v>39</v>
+      </c>
+      <c r="F13">
+        <f>F12+2</f>
+        <v>32</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <f>B13*2</f>
+        <v>400</v>
+      </c>
+      <c r="C14">
+        <v>291</v>
+      </c>
+      <c r="F14">
+        <f t="shared" ref="F14:F16" si="0">F13+2</f>
+        <v>34</v>
+      </c>
+      <c r="G14" s="1">
+        <v>6455</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <f>B14*2</f>
+        <v>800</v>
+      </c>
+      <c r="C15">
+        <v>2305</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="G15" s="1">
+        <v>20543</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>B15*2</f>
+        <v>1600</v>
+      </c>
+      <c r="C16">
+        <v>18369</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>1000</v>
+      </c>
+      <c r="C21" s="1">
+        <v>10</v>
+      </c>
+      <c r="F21">
+        <v>1000</v>
+      </c>
+      <c r="G21" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <f>B21*2</f>
+        <v>2000</v>
+      </c>
+      <c r="C22" s="1">
+        <v>39</v>
+      </c>
+      <c r="F22">
+        <f>F21*2</f>
+        <v>2000</v>
+      </c>
+      <c r="G22" s="1">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <f>B22*2</f>
+        <v>4000</v>
+      </c>
+      <c r="C23" s="1">
+        <v>150</v>
+      </c>
+      <c r="F23">
+        <f>F22*2</f>
+        <v>4000</v>
+      </c>
+      <c r="G23" s="1">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <f>B23*2</f>
+        <v>8000</v>
+      </c>
+      <c r="C24" s="1">
+        <v>584</v>
+      </c>
+      <c r="F24">
+        <f>F23*2</f>
+        <v>8000</v>
+      </c>
+      <c r="G24" s="1">
+        <v>3723</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <f>B24*2</f>
+        <v>16000</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2329</v>
+      </c>
+      <c r="F25">
+        <f>F24*2</f>
+        <v>16000</v>
+      </c>
+      <c r="G25" s="1">
+        <v>15398</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B26">
+        <f>B25*2</f>
+        <v>32000</v>
+      </c>
+      <c r="C26" s="1">
+        <v>9340</v>
+      </c>
+      <c r="F26">
+        <f>F25*2</f>
+        <v>32000</v>
+      </c>
+      <c r="G26" s="1">
+        <v>50938</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <f>B26*2</f>
+        <v>64000</v>
+      </c>
+      <c r="C27" s="1">
+        <v>37188</v>
+      </c>
+      <c r="F27">
+        <f>F26*2</f>
+        <v>64000</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <f>B27*2</f>
+        <v>128000</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <f>F27*2</f>
+        <v>128000</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>100000</v>
+      </c>
+      <c r="B34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" t="s">
+        <v>8</v>
+      </c>
+      <c r="J34" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G35" t="s">
+        <v>0</v>
+      </c>
+      <c r="H35" t="s">
+        <v>1</v>
+      </c>
+      <c r="K35" t="s">
+        <v>0</v>
+      </c>
+      <c r="L35" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C36">
+        <v>3</v>
+      </c>
+      <c r="D36">
+        <v>10</v>
+      </c>
+      <c r="G36">
+        <v>3</v>
+      </c>
+      <c r="H36">
+        <v>56</v>
+      </c>
+      <c r="K36">
+        <v>3</v>
+      </c>
+      <c r="L36">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C37">
+        <f>C36*2</f>
+        <v>6</v>
+      </c>
+      <c r="D37">
+        <v>17</v>
+      </c>
+      <c r="G37">
+        <f>G36*2</f>
+        <v>6</v>
+      </c>
+      <c r="H37">
+        <v>79</v>
+      </c>
+      <c r="K37">
+        <f>K36*2</f>
+        <v>6</v>
+      </c>
+      <c r="L37">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C38">
+        <f t="shared" ref="C38:C46" si="1">C37*2</f>
+        <v>12</v>
+      </c>
+      <c r="D38">
+        <v>30</v>
+      </c>
+      <c r="G38">
+        <f t="shared" ref="G38:G46" si="2">G37*2</f>
+        <v>12</v>
+      </c>
+      <c r="H38">
+        <v>135</v>
+      </c>
+      <c r="K38">
+        <f t="shared" ref="K38:K46" si="3">K37*2</f>
+        <v>12</v>
+      </c>
+      <c r="L38">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C39">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="D39">
+        <v>56</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="H39">
+        <v>233</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="L39">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C40">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="D40">
+        <v>106</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="2"/>
+        <v>48</v>
+      </c>
+      <c r="H40">
+        <v>424</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="L40">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C41">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="D41">
+        <v>223</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="2"/>
+        <v>96</v>
+      </c>
+      <c r="H41">
+        <v>812</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="3"/>
+        <v>96</v>
+      </c>
+      <c r="L41">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C42">
+        <f t="shared" si="1"/>
+        <v>192</v>
+      </c>
+      <c r="D42">
+        <v>462</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="2"/>
+        <v>192</v>
+      </c>
+      <c r="H42">
+        <v>1593</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="3"/>
+        <v>192</v>
+      </c>
+      <c r="L42">
+        <v>4668</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C43">
+        <f t="shared" si="1"/>
+        <v>384</v>
+      </c>
+      <c r="D43">
+        <v>970</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="2"/>
+        <v>384</v>
+      </c>
+      <c r="H43">
+        <v>3141</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="3"/>
+        <v>384</v>
+      </c>
+      <c r="L43">
+        <v>9714</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C44">
+        <f t="shared" si="1"/>
+        <v>768</v>
+      </c>
+      <c r="D44">
+        <v>2023</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="2"/>
+        <v>768</v>
+      </c>
+      <c r="H44">
+        <v>6313</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="3"/>
+        <v>768</v>
+      </c>
+      <c r="L44">
+        <v>20795</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C45">
+        <f t="shared" si="1"/>
+        <v>1536</v>
+      </c>
+      <c r="D45">
+        <v>4192</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="2"/>
+        <v>1536</v>
+      </c>
+      <c r="H45">
+        <v>12525</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="3"/>
+        <v>1536</v>
+      </c>
+      <c r="L45">
+        <v>41384</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C46">
+        <f t="shared" si="1"/>
+        <v>3072</v>
+      </c>
+      <c r="D46">
+        <v>8509</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="2"/>
+        <v>3072</v>
+      </c>
+      <c r="H46">
+        <v>24949</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="3"/>
+        <v>3072</v>
+      </c>
+      <c r="L46" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C47">
+        <f>C46*2</f>
+        <v>6144</v>
+      </c>
+      <c r="D47">
+        <v>17387</v>
+      </c>
+      <c r="G47">
+        <f>G46*2</f>
+        <v>6144</v>
+      </c>
+      <c r="H47">
+        <v>49878</v>
+      </c>
+      <c r="K47">
+        <f>K46*2</f>
+        <v>6144</v>
+      </c>
+      <c r="L47" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" t="s">
+        <v>12</v>
+      </c>
+      <c r="G52" t="s">
+        <v>13</v>
+      </c>
+      <c r="I52" t="s">
+        <v>12</v>
+      </c>
+      <c r="J52" t="s">
+        <v>13</v>
+      </c>
+      <c r="L52" t="s">
+        <v>12</v>
+      </c>
+      <c r="M52" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C53">
+        <v>10</v>
+      </c>
+      <c r="D53">
+        <v>56</v>
+      </c>
+      <c r="F53">
+        <v>10</v>
+      </c>
+      <c r="G53">
+        <v>73</v>
+      </c>
+      <c r="I53">
+        <v>10</v>
+      </c>
+      <c r="J53">
+        <v>107</v>
+      </c>
+      <c r="L53">
+        <v>10</v>
+      </c>
+      <c r="M53">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C54">
+        <v>11</v>
+      </c>
+      <c r="D54">
+        <v>56</v>
+      </c>
+      <c r="F54">
+        <v>11</v>
+      </c>
+      <c r="G54">
+        <v>76</v>
+      </c>
+      <c r="I54">
+        <v>11</v>
+      </c>
+      <c r="J54">
+        <v>111</v>
+      </c>
+      <c r="L54">
+        <v>11</v>
+      </c>
+      <c r="M54">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C55">
+        <v>12</v>
+      </c>
+      <c r="D55">
+        <v>59</v>
+      </c>
+      <c r="F55">
+        <v>12</v>
+      </c>
+      <c r="G55">
+        <v>82</v>
+      </c>
+      <c r="I55">
+        <v>12</v>
+      </c>
+      <c r="J55">
+        <v>114</v>
+      </c>
+      <c r="L55">
+        <v>12</v>
+      </c>
+      <c r="M55">
+        <v>3680</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C56">
+        <v>13</v>
+      </c>
+      <c r="D56">
+        <v>63</v>
+      </c>
+      <c r="F56">
+        <v>13</v>
+      </c>
+      <c r="G56">
+        <v>88</v>
+      </c>
+      <c r="I56">
+        <v>13</v>
+      </c>
+      <c r="J56">
+        <v>125</v>
+      </c>
+      <c r="L56">
+        <v>13</v>
+      </c>
+      <c r="M56">
+        <v>5832</v>
+      </c>
+    </row>
+    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C57">
+        <v>14</v>
+      </c>
+      <c r="D57">
+        <v>66</v>
+      </c>
+      <c r="F57">
+        <v>14</v>
+      </c>
+      <c r="G57">
+        <v>92</v>
+      </c>
+      <c r="I57">
+        <v>14</v>
+      </c>
+      <c r="J57">
+        <v>128</v>
+      </c>
+      <c r="L57">
+        <v>14</v>
+      </c>
+      <c r="M57">
+        <v>9104</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C58">
+        <v>15</v>
+      </c>
+      <c r="D58">
+        <v>72</v>
+      </c>
+      <c r="F58">
+        <v>15</v>
+      </c>
+      <c r="G58">
+        <v>98</v>
+      </c>
+      <c r="I58">
+        <v>15</v>
+      </c>
+      <c r="J58">
+        <v>135</v>
+      </c>
+      <c r="L58">
+        <v>15</v>
+      </c>
+      <c r="M58">
+        <v>14528</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C59">
+        <v>16</v>
+      </c>
+      <c r="D59">
+        <v>75</v>
+      </c>
+      <c r="F59">
+        <v>16</v>
+      </c>
+      <c r="G59">
+        <v>104</v>
+      </c>
+      <c r="I59">
+        <v>16</v>
+      </c>
+      <c r="J59">
+        <v>143</v>
+      </c>
+      <c r="L59">
+        <v>16</v>
+      </c>
+      <c r="M59">
+        <v>34132</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C60">
+        <v>17</v>
+      </c>
+      <c r="D60">
+        <v>76</v>
+      </c>
+      <c r="F60">
+        <v>17</v>
+      </c>
+      <c r="G60">
+        <v>110</v>
+      </c>
+      <c r="I60">
+        <v>17</v>
+      </c>
+      <c r="J60">
+        <v>153</v>
+      </c>
+      <c r="L60">
+        <v>17</v>
+      </c>
+      <c r="M60" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C61">
+        <v>18</v>
+      </c>
+      <c r="D61">
+        <v>82</v>
+      </c>
+      <c r="F61">
+        <v>18</v>
+      </c>
+      <c r="G61">
+        <v>118</v>
+      </c>
+      <c r="I61">
+        <v>18</v>
+      </c>
+      <c r="J61">
+        <v>160</v>
+      </c>
+      <c r="L61">
+        <v>18</v>
+      </c>
+      <c r="M61" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C62">
+        <v>19</v>
+      </c>
+      <c r="D62">
+        <v>85</v>
+      </c>
+      <c r="F62">
+        <v>19</v>
+      </c>
+      <c r="G62">
+        <v>123</v>
+      </c>
+      <c r="I62">
+        <v>19</v>
+      </c>
+      <c r="J62">
+        <v>168</v>
+      </c>
+      <c r="L62">
+        <v>19</v>
+      </c>
+      <c r="M62" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C63">
+        <v>20</v>
+      </c>
+      <c r="D63">
+        <v>89</v>
+      </c>
+      <c r="F63">
+        <v>20</v>
+      </c>
+      <c r="G63">
+        <v>128</v>
+      </c>
+      <c r="I63">
+        <v>20</v>
+      </c>
+      <c r="J63">
+        <v>175</v>
+      </c>
+      <c r="L63">
+        <v>20</v>
+      </c>
+      <c r="M63" t="s">
         <v>2</v>
       </c>
     </row>
